--- a/UAT_Excel_Reports/Bbu By Product Weekly_UAT.xlsx
+++ b/UAT_Excel_Reports/Bbu By Product Weekly_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,26 +496,39 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>--- INITIAL NAVIGATION TO EXECUTIVE DASHBOARD ---</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C.1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Navigate to the 'Executive Dashboard' in the demand planning application by entering the specified URL.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>`page.goto("https://stage.bbu.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=4&amp;tabIndex=2")`</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>C.1</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the 'Executive Dashboard' in the demand planning application by entering the specified URL.</t>
+          <t>Click on the 'Product Total columns (0)' button to open the column configuration panel.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`page.goto("https://stage.bbu.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=4&amp;tabIndex=2")`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -523,26 +536,39 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>--- COLUMN CONFIGURATION - PRODUCT TOTAL ---</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>D.2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Uncheck the 'System Forecast Total (Plan Week)' column to hide it from the view.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle").uncheck()`</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>D.3</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product Total columns (0)' button to open the column configuration panel.</t>
+          <t>Uncheck the 'System Forecast Base (Plan)' column to hide it from the view.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -552,17 +578,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>D.2</t>
+          <t>D.4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'System Forecast Total (Plan Week)' column to hide it from the view.</t>
+          <t>Uncheck the 'System Forecast Promotion (' column to hide it from the view.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (").get_by_label("Press SPACE to toggle").uncheck()`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -572,17 +598,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>D.3</t>
+          <t>D.5</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'System Forecast Base (Plan)' column to hide it from the view.</t>
+          <t>Click on the third column selector in the configuration panel to modify its settings.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
@@ -592,12 +618,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>D.4</t>
+          <t>D.6</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'System Forecast Promotion (' column to hide it from the view.</t>
+          <t>Uncheck the 'System Forecast Promotion (' column again to ensure it is hidden.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -612,17 +638,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>D.5</t>
+          <t>D.7</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Click on the third column selector in the configuration panel to modify its settings.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr"/>
@@ -632,17 +658,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>D.6</t>
+          <t>D.8</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'System Forecast Promotion (' column again to ensure it is hidden.</t>
+          <t>Click on the first adjustment option to apply changes to the column configuration.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (").get_by_label("Press SPACE to toggle").uncheck()`</t>
+          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -652,17 +678,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>D.7</t>
+          <t>D.9</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
+          <t>Click on the 'Save Preference' button to save the updated column configuration.</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
@@ -672,17 +698,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>D.8</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Click on the first adjustment option to apply changes to the column configuration.</t>
+          <t>Click on the first download button (identified by the '.icon-color-toolbar-active.zeb-download-underline' class) to initiate the file download.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
+          <t>`page.locator(".icon-color-toolbar-active.zeb-download-underline").first.click()`</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -692,17 +718,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>D.9</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Save Preference' button to save the updated column configuration.</t>
+          <t>Click on the first adjustments button (identified by the '.pointer.zeb-adjustments' class) to open the adjustments menu.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
+          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -710,26 +736,39 @@
       <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>--- FILE DOWNLOAD - EXECUTIVE DASHBOARD ---</t>
-        </is>
-      </c>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>F.2</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Reset Preference' option from the menu to reset all preferences to their default state.</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Click on the first download button (identified by the '.icon-color-toolbar-active.zeb-download-underline' class) to initiate the file download.</t>
+          <t>Navigate to the 'Products' tab by clicking on the 'Products' option to access the product configuration section.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".icon-color-toolbar-active.zeb-download-underline").first.click()`</t>
+          <t>`page.get_by_text("Products").click()`</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -737,26 +776,39 @@
       <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>--- RESET PREFERENCES AND NAVIGATE TO PRODUCTS TAB ---</t>
-        </is>
-      </c>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>G.1</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Open the 'Products columns' configuration menu by clicking the button within the 'esp-card-component' element labeled 'Products columns (0)'.</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Click on the first adjustments button (identified by the '.pointer.zeb-adjustments' class) to open the adjustments menu.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -766,17 +818,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Reset Preference' option from the menu to reset all preferences to their default state.</t>
+          <t>Enable visibility for the 'System Forecast Total (Plan Week)' column by checking its corresponding checkbox.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -786,17 +838,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>F.3</t>
+          <t>G.4</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the 'Products' tab by clicking on the 'Products' option to access the product configuration section.</t>
+          <t>Enable visibility for the 'System Forecast Base (Plan Week)' column by checking its corresponding checkbox.</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Products").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -804,26 +856,39 @@
       <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>--- COLUMN CONFIGURATION - PRODUCTS ---</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>G.5</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Enable visibility for the 'System Forecast Promotion (Plan Week)' column by checking its corresponding checkbox.</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Open the 'Products columns' configuration menu by clicking the button within the 'esp-card-component' element labeled 'Products columns (0)'.</t>
+          <t>Enable visibility for the 'System Forecast Total (Plan+1)' column by checking its corresponding checkbox.</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -833,17 +898,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>G.7</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
+          <t>Enable visibility for the 'System Forecast Base (Plan+1)' column by checking its corresponding checkbox.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -853,17 +918,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>G.8</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Total (Plan Week)' column by checking its corresponding checkbox.</t>
+          <t>Enable visibility for the 'System Forecast Promotion (Plan+1 Week)' column by checking its corresponding checkbox.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan+1 Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -873,17 +938,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>G.9</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Base (Plan Week)' column by checking its corresponding checkbox.</t>
+          <t>Enable visibility for the 'Week Gross Units Average' column by checking its corresponding checkbox.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="Week Gross Units Average Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -893,17 +958,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>G.10</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Promotion (Plan Week)' column by checking its corresponding checkbox.</t>
+          <t>Enable visibility for the '6 Week Aged Net Units Average' column by checking its corresponding checkbox.</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="6 Week Aged Net Units Average Column", exact=True).get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
@@ -913,17 +978,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>G.6</t>
+          <t>G.11</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Total (Plan+1)' column by checking its corresponding checkbox.</t>
+          <t>Recheck the 'Toggle All Columns Visibility' checkbox to ensure all selected columns are visible.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -933,17 +998,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>G.7</t>
+          <t>G.12</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Base (Plan+1)' column by checking its corresponding checkbox.</t>
+          <t>Click on the preferences dropdown menu to access options for saving or resetting preferences.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -953,17 +1018,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>G.8</t>
+          <t>G.13</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Promotion (Plan+1 Week)' column by checking its corresponding checkbox.</t>
+          <t>Select the 'Save Preference' option to save the current column visibility settings.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan+1 Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
@@ -973,17 +1038,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G.9</t>
+          <t>G.14</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'Week Gross Units Average' column by checking its corresponding checkbox.</t>
+          <t>Reopen the preferences dropdown menu to access the reset option.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Week Gross Units Average Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -993,17 +1058,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>G.10</t>
+          <t>G.15</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the '6 Week Aged Net Units Average' column by checking its corresponding checkbox.</t>
+          <t>Select the 'Reset Preference' option to revert to the default column visibility settings.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="6 Week Aged Net Units Average Column", exact=True).get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -1013,17 +1078,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>G.11</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Recheck the 'Toggle All Columns Visibility' checkbox to ensure all selected columns are visible.</t>
+          <t>Click on the filter icon in the header to open the filter options for the column.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1033,17 +1098,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>G.12</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Click on the preferences dropdown menu to access options for saving or resetting preferences.</t>
+          <t>Enter the filter value 'BARCEL' into the textbox to filter the column data.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("BARCEL")`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1053,17 +1118,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>G.13</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Save Preference' option to save the current column visibility settings.</t>
+          <t>Click on the 'Apply' button to apply the filter and update the displayed data.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
+          <t>`page.get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1073,17 +1138,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>G.14</t>
+          <t>H.4</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Reopen the preferences dropdown menu to access the reset option.</t>
+          <t>Click on the filter icon in the header again to reopen the filter options.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1093,17 +1158,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>G.15</t>
+          <t>H.5</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Reset Preference' option to revert to the default column visibility settings.</t>
+          <t>Click on the 'Reset' button to clear the filter and revert the column data to its default state.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1111,26 +1176,39 @@
       <c r="F36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>--- FILTER AND PAGINATION ACTIONS ---</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>H.6</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Select the row with the name 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>H.7</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon in the header to open the filter options for the column.</t>
+          <t>Navigate to the second page of the table by clicking on the pagination link labeled '2'.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
+          <t>`page.locator("a").filter(has_text="2").click()`</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1140,17 +1218,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>H.2</t>
+          <t>H.8</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Enter the filter value 'BARCEL' into the textbox to filter the column data.</t>
+          <t>Navigate to the third page of the table by clicking on the pagination link labeled '3'.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("BARCEL")`</t>
+          <t>`page.locator("a").filter(has_text="3").click()`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1160,17 +1238,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>H.3</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the filter and update the displayed data.</t>
+          <t>Click on the fourth item in the list to select it.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("listitem").filter(has_text=re.compile(r"^$")).nth(4).click()`</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
@@ -1180,17 +1258,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>H.4</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon in the header again to reopen the filter options.</t>
+          <t>Click on the first dropdown caret to open the dropdown menu.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
+          <t>`page.locator(".dropdown-caret.p-l-16").first.click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1200,17 +1278,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>H.5</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Reset' button to clear the filter and revert the column data to its default state.</t>
+          <t>Select the option 'View 20 row(s)' from the dropdown menu to adjust the number of rows displayed.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1220,17 +1298,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>H.6</t>
+          <t>I.4</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Select the row with the name 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
+          <t>Click on the 'Filter' button to open the filter options.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
+          <t>`page.get_by_text("Filter").click()`</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
@@ -1240,17 +1318,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>H.7</t>
+          <t>I.5</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the second page of the table by clicking on the pagination link labeled '2'.</t>
+          <t>Click on the dropdown caret within the filter section to open the time filter options.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="2").click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1260,17 +1338,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>H.8</t>
+          <t>I.6</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the third page of the table by clicking on the pagination link labeled '3'.</t>
+          <t>Select the 'Latest 5 Next 4' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="3").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1278,26 +1356,39 @@
       <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>--- DROPDOWN AND MULTI-SELECT ACTIONS ---</t>
-        </is>
-      </c>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>I.7</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>I.8</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Click on the fourth item in the list to select it.</t>
+          <t>Select the 'Latest 5 Next 12' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("listitem").filter(has_text=re.compile(r"^$")).nth(4).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 12$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1307,17 +1398,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>I.9</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown caret to open the dropdown menu.</t>
+          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".dropdown-caret.p-l-16").first.click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1327,17 +1418,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>I.10</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Select the option 'View 20 row(s)' from the dropdown menu to adjust the number of rows displayed.</t>
+          <t>Select the 'Latest 13 Next 4' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1347,17 +1438,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>I.11</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter' button to open the filter options.</t>
+          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Filter").click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1367,17 +1458,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>I.5</t>
+          <t>I.12</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret within the filter section to open the time filter options.</t>
+          <t>Select the 'Latest 13 Next 12' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 12$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1387,17 +1478,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>I.6</t>
+          <t>I.13</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 5 Next 4' option from the time filter dropdown.</t>
+          <t>Click on the dropdown caret to open the multi-select dropdown menu.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 4$")).nth(1).click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1407,17 +1498,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>I.7</t>
+          <t>I.14</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
+          <t>Click on the first option in the dropdown menu to select it.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1427,17 +1518,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>I.8</t>
+          <t>I.15</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 5 Next 12' option from the time filter dropdown.</t>
+          <t>Click on the first option under the 'dropdown-option' class to select it.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 12$")).nth(1).click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
@@ -1447,17 +1538,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>I.9</t>
+          <t>I.16</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
+          <t>Click on the second option in the dropdown menu to select it.</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1467,17 +1558,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>I.10</t>
+          <t>I.17</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 13 Next 4' option from the time filter dropdown.</t>
+          <t>Click on the third option in the dropdown menu to select it.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 4$")).nth(1).click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(3) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1487,17 +1578,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>I.11</t>
+          <t>I.18</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
+          <t>Click on the fourth option in the dropdown menu to select it.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1507,17 +1598,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>I.12</t>
+          <t>I.19</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 13 Next 12' option from the time filter dropdown.</t>
+          <t>Click on the fifth option in the dropdown menu to select it.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 12$")).nth(1).click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1527,17 +1618,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>I.13</t>
+          <t>I.20</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to open the multi-select dropdown menu.</t>
+          <t>Click on the sixth option in the dropdown menu to select it.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(6)").click()`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1547,12 +1638,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>I.14</t>
+          <t>I.21</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Click on the first option in the dropdown menu to select it.</t>
+          <t>Click on the first option in the dropdown menu again to deselect it.</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1567,17 +1658,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>I.15</t>
+          <t>J.1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Click on the first option under the 'dropdown-option' class to select it.</t>
+          <t>Click on the dropdown caret to open the multi-select dropdown menu for column visibility options.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1587,17 +1678,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>I.16</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Click on the second option in the dropdown menu to select it.</t>
+          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card to expand or collapse the product details.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1607,17 +1698,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>I.17</t>
+          <t>J.3</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Click on the third option in the dropdown menu to select it.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns in the Weekly Summary table.</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(3) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
@@ -1627,17 +1718,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>I.18</t>
+          <t>J.4</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Click on the fourth option in the dropdown menu to select it.</t>
+          <t>Check the visibility of the column labeled '-10-26 (44)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="-10-26 (44) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -1647,17 +1738,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>I.19</t>
+          <t>J.5</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth option in the dropdown menu to select it.</t>
+          <t>Check the visibility of the column labeled '-11-02 (45)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="-11-02 (45) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1667,17 +1758,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>I.20</t>
+          <t>J.6</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Click on the sixth option in the dropdown menu to select it.</t>
+          <t>Check the visibility of the column labeled '-11-09 (46)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(6)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="-11-09 (46) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -1687,17 +1778,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>I.21</t>
+          <t>J.7</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Click on the first option in the dropdown menu again to deselect it.</t>
+          <t>Check the visibility of the column labeled '-11-16 (47)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="-11-16 (47) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -1705,26 +1796,39 @@
       <c r="F67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>--- WEEKLY SUMMARY PRODUCT CONFIGURATION ---</t>
-        </is>
-      </c>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>J.8</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Recheck the 'Toggle All Columns Visibility' checkbox to make all columns visible again in the Weekly Summary table.</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>J.1</t>
+          <t>J.9</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to open the multi-select dropdown menu for column visibility options.</t>
+          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card again to collapse the product details.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -1734,17 +1838,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>K.1</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card to expand or collapse the product details.</t>
+          <t>Click on the 'Preference' icon to open the dropdown menu for managing preferences.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
+          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -1754,17 +1858,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>J.3</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns in the Weekly Summary table.</t>
+          <t>Click on the 'Save Preference' button to save the current table preferences.</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.get_by_text("Save Preference").click()`</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -1774,17 +1878,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>J.4</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility of the column labeled '-10-26 (44)' by toggling its checkbox.</t>
+          <t>Click on the 'Export' icon to initiate the export process for the table data.</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="-10-26 (44) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -1794,17 +1898,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>J.5</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility of the column labeled '-11-02 (45)' by toggling its checkbox.</t>
+          <t>Click on the 'Preference' dropdown to open the menu for managing preferences.</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="-11-02 (45) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr"/>
@@ -1814,17 +1918,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>J.6</t>
+          <t>K.5</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility of the column labeled '-11-09 (46)' by toggling its checkbox.</t>
+          <t>Select 'Reset Preference' from the dropdown to reset the table preferences to default.</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="-11-09 (46) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -1834,17 +1938,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>J.7</t>
+          <t>K.6</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility of the column labeled '-11-16 (47)' by toggling its checkbox.</t>
+          <t>Click on the date '-02-15 (08)' to select it from the available options.</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="-11-16 (47) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("-02-15 (08)").click()`</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
@@ -1854,17 +1958,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>J.8</t>
+          <t>K.7</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Recheck the 'Toggle All Columns Visibility' checkbox to make all columns visible again in the Weekly Summary table.</t>
+          <t>Click on the fifth image element to initiate the column visibility settings.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.get_by_role("img").nth(5).click()`</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
@@ -1874,17 +1978,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>J.9</t>
+          <t>K.8</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card again to collapse the product details.</t>
+          <t>Click on the button within the 'Event Details columns (0)' card to open the column visibility options.</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Event Details columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
@@ -1892,26 +1996,39 @@
       <c r="F77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>--- PREFERENCE MANAGEMENT AND EXPORT ACTIONS ---</t>
-        </is>
-      </c>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>K.9</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Uncheck the 'Event Column' to hide it from the table.</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>K.1</t>
+          <t>K.10</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' icon to open the dropdown menu for managing preferences.</t>
+          <t>Uncheck the 'UPC 12 Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("treeitem", name="UPC 12 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
@@ -1921,17 +2038,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>K.2</t>
+          <t>K.11</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Save Preference' button to save the current table preferences.</t>
+          <t>Uncheck the 'Customer Level 2 Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Customer Level 2 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -1941,17 +2058,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>K.12</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Export' icon to initiate the export process for the table data.</t>
+          <t>Uncheck the 'Start Date Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Start Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -1961,17 +2078,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>K.13</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' dropdown to open the menu for managing preferences.</t>
+          <t>Uncheck the 'End Date Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("treeitem", name="End Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -1981,17 +2098,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>K.5</t>
+          <t>K.14</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Select 'Reset Preference' from the dropdown to reset the table preferences to default.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
@@ -2001,17 +2118,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>K.6</t>
+          <t>K.15</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Click on the date '-02-15 (08)' to select it from the available options.</t>
+          <t>Click on the 'Preference' icon to open the dropdown menu for saving or resetting preferences.</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("-02-15 (08)").click()`</t>
+          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -2021,17 +2138,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>K.7</t>
+          <t>K.16</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth image element to initiate the column visibility settings.</t>
+          <t>Click on 'Save Preference' to save the current column visibility settings.</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("img").nth(5).click()`</t>
+          <t>`page.get_by_text("Save Preference").click()`</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr"/>
@@ -2041,17 +2158,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>K.8</t>
+          <t>K.17</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Event Details columns (0)' card to open the column visibility options.</t>
+          <t>Click on the 'Export' icon to export the data with the current preferences.</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Event Details columns (0)").get_by_role("button").click()`</t>
+          <t>`page.locator("div:nth-child(6) &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2061,17 +2178,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>K.9</t>
+          <t>L.1</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Event Column' to hide it from the table.</t>
+          <t>Click on the 'Preference' icon to open the dropdown menu for resetting preferences.</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
@@ -2081,17 +2198,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>K.10</t>
+          <t>L.2</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'UPC 12 Column' to hide it from the table.</t>
+          <t>Click on 'Reset Preference' to revert to the default column visibility settings.</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="UPC 12 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
@@ -2101,17 +2218,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>K.11</t>
+          <t>M.1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Customer Level 2 Column' to hide it from the table.</t>
+          <t>Click on the filter icon in the column header to open the filter options.</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Customer Level 2 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .ag-icon").click()`</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
@@ -2121,17 +2238,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>K.12</t>
+          <t>M.2</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Start Date Column' to hide it from the table.</t>
+          <t>Enter 'Scan Track' into the filter textbox to filter the data based on this value.</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Start Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("Scan Track")`</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
@@ -2141,17 +2258,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>K.13</t>
+          <t>M.3</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'End Date Column' to hide it from the table.</t>
+          <t>Click on the 'Apply' button to apply the filter and update the displayed data.</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="End Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
@@ -2161,17 +2278,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>K.14</t>
+          <t>M.4</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
+          <t>Click on the active filter icon to open the filter options for resetting.</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button.ag-filter-active &gt; .ag-icon").click()`</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr"/>
@@ -2181,17 +2298,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>K.15</t>
+          <t>M.5</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' icon to open the dropdown menu for saving or resetting preferences.</t>
+          <t>Click on the 'Reset' button to clear the applied filter and restore the unfiltered data.</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
@@ -2201,17 +2318,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>K.16</t>
+          <t>N.1</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Save Preference' to save the current column visibility settings.</t>
+          <t>Click on the 'Products' tab to navigate to the product selection view.</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
+          <t>`page.get_by_text("Products").click()`</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
@@ -2221,17 +2338,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>K.17</t>
+          <t>N.2</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Export' icon to export the data with the current preferences.</t>
+          <t>Double-click on the product 'ARNOLD-BRWNBRY-OROWT' to drill down into its details.</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(6) &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
+          <t>`page.locator("span").filter(has_text="ARNOLD-BRWNBRY-OROWT").first.dblclick()`</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
@@ -2239,26 +2356,39 @@
       <c r="F95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>--- EVENT DETAILS COLUMN CONFIGURATION ---</t>
-        </is>
-      </c>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>N.3</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Double-click on 'ABO COUNTRY' to further drill down into its details.</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.dblclick()`</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>L.1</t>
+          <t>N.4</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' icon to open the dropdown menu for resetting preferences.</t>
+          <t>Click on 'ABO COUNTRY' to select it.</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click()`</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
@@ -2268,17 +2398,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>L.2</t>
+          <t>N.5</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Reset Preference' to revert to the default column visibility settings.</t>
+          <t>Double-click on the second instance of 'ABO COUNTRY' to drill down further.</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.get_by_text("ABO COUNTRY").nth(1).dblclick()`</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
@@ -2286,26 +2416,39 @@
       <c r="F98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>--- FILTER ACTIONS - SCAN TRACK ---</t>
-        </is>
-      </c>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>N.6</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Right-click on the product 'OR CTY BTRMK WP 24Z-731300012500' to open the context menu.</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text=re.compile(r"^OR CTY BTRMK WP 24Z-731300012500$")).click(button="right")`</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>M.1</t>
+          <t>N.7</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon in the column header to open the filter options.</t>
+          <t>Click on 'Drill up' from the context menu to navigate back to the previous level.</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .ag-icon").click()`</t>
+          <t>`page.get_by_text("Drill up").click()`</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -2315,17 +2458,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>M.2</t>
+          <t>N.8</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Enter 'Scan Track' into the filter textbox to filter the data based on this value.</t>
+          <t>Right-click on 'ABO COUNTRY' to open the context menu again.</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("Scan Track")`</t>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
@@ -2335,17 +2478,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>M.3</t>
+          <t>N.9</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the filter and update the displayed data.</t>
+          <t>Click on 'Drill up' from the context menu to navigate back another level.</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_text("Drill up").click()`</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
@@ -2355,17 +2498,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>M.4</t>
+          <t>N.10</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Click on the active filter icon to open the filter options for resetting.</t>
+          <t>Right-click on 'ABO COUNTRY' to open the context menu once more.</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button.ag-filter-active &gt; .ag-icon").click()`</t>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
@@ -2375,17 +2518,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>M.5</t>
+          <t>N.11</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Reset' button to clear the applied filter and restore the unfiltered data.</t>
+          <t>Click on 'Drill up' from the context menu to return to the top level.</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
+          <t>`page.get_by_text("Drill up").click()`</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
@@ -2393,26 +2536,39 @@
       <c r="F104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>--- PRODUCT DRILL-DOWN AND CONTEXT MENU ACTIONS ---</t>
-        </is>
-      </c>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>O.1</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Select the row for the product 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr"/>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>N.1</t>
+          <t>O.2</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Products' tab to navigate to the product selection view.</t>
+          <t>Close the current page after completing the row selection.</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Products").click()`</t>
+          <t>`page.close()`</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr"/>
@@ -2422,17 +2578,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>N.2</t>
+          <t>O.3</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Double-click on the product 'ARNOLD-BRWNBRY-OROWT' to drill down into its details.</t>
+          <t>Close the browser context to clean up resources.</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="ARNOLD-BRWNBRY-OROWT").first.dblclick()`</t>
+          <t>`context.close()`</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr"/>
@@ -2442,286 +2598,26 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>N.3</t>
+          <t>O.4</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Double-click on 'ABO COUNTRY' to further drill down into its details.</t>
+          <t>Close the browser to end the session.</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.dblclick()`</t>
+          <t>`browser.close()`</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr"/>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>N.4</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Click on 'ABO COUNTRY' to select it.</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click()`</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr"/>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>N.5</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Double-click on the second instance of 'ABO COUNTRY' to drill down further.</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("ABO COUNTRY").nth(1).dblclick()`</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr"/>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>N.6</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Right-click on the product 'OR CTY BTRMK WP 24Z-731300012500' to open the context menu.</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("span").filter(has_text=re.compile(r"^OR CTY BTRMK WP 24Z-731300012500$")).click(button="right")`</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr"/>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>N.7</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>Click on 'Drill up' from the context menu to navigate back to the previous level.</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Drill up").click()`</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr"/>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>N.8</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Right-click on 'ABO COUNTRY' to open the context menu again.</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr"/>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>N.9</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>Click on 'Drill up' from the context menu to navigate back another level.</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Drill up").click()`</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr"/>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>N.10</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Right-click on 'ABO COUNTRY' to open the context menu once more.</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr"/>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>N.11</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Click on 'Drill up' from the context menu to return to the top level.</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Drill up").click()`</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr"/>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>--- ROW SELECTION AND CLEANUP ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>O.1</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Select the row for the product 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr"/>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>O.2</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Close the current page after completing the row selection.</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>`page.close()`</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr"/>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>O.3</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>Close the browser context to clean up resources.</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>`context.close()`</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr"/>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>O.4</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Close the browser to end the session.</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>`browser.close()`</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr"/>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A105:F105"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UAT_Excel_Reports/Bbu By Product Weekly_UAT.xlsx
+++ b/UAT_Excel_Reports/Bbu By Product Weekly_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,39 +496,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>C.1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Navigate to the 'Executive Dashboard' in the demand planning application by entering the specified URL.</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>`page.goto("https://stage.bbu.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=4&amp;tabIndex=2")`</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>--- NAVIGATE TO EXECUTIVE DASHBOARD ---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>C.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product Total columns (0)' button to open the column configuration panel.</t>
+          <t>Open the 'Executive Dashboard' by navigating to the specified URL in the demand planning application.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
+          <t>`page.goto("https://stage.bbu.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=4&amp;tabIndex=2")`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -536,39 +523,26 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>D.2</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Uncheck the 'System Forecast Total (Plan Week)' column to hide it from the view.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle").uncheck()`</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN CONFIGURATION - INITIAL ADJUSTMENTS ---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>D.3</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'System Forecast Base (Plan)' column to hide it from the view.</t>
+          <t>Click on the 'Product Total columns (0)' button to open the column configuration panel.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -578,17 +552,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>D.4</t>
+          <t>D.2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'System Forecast Promotion (' column to hide it from the view.</t>
+          <t>Uncheck the 'System Forecast Total (Plan Week)' column to hide it from the view.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (").get_by_label("Press SPACE to toggle").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle").uncheck()`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -598,17 +572,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>D.5</t>
+          <t>D.3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Click on the third column selector in the configuration panel to modify its settings.</t>
+          <t>Uncheck the 'System Forecast Base (Plan)' column to hide it from the view.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
@@ -618,12 +592,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>D.6</t>
+          <t>D.4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'System Forecast Promotion (' column again to ensure it is hidden.</t>
+          <t>Uncheck the 'System Forecast Promotion (' column to hide it from the view.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -638,17 +612,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>D.7</t>
+          <t>D.5</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
+          <t>Click on the third column selector in the configuration panel to modify its settings.</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr"/>
@@ -658,17 +632,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>D.8</t>
+          <t>D.6</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Click on the first adjustment option to apply changes to the column configuration.</t>
+          <t>Uncheck the 'System Forecast Promotion (' column again to ensure it is hidden.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (").get_by_label("Press SPACE to toggle").uncheck()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -676,24 +650,11 @@
       <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>D.9</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Save Preference' button to save the updated column configuration.</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>--- TOGGLE ALL COLUMNS VISIBILITY ---</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -703,12 +664,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Click on the first download button (identified by the '.icon-color-toolbar-active.zeb-download-underline' class) to initiate the file download.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".icon-color-toolbar-active.zeb-download-underline").first.click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -716,39 +677,26 @@
       <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>F.1</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first adjustments button (identified by the '.pointer.zeb-adjustments' class) to open the adjustments menu.</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>--- SAVE PREFERENCES AND DOWNLOAD FILE ---</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Reset Preference' option from the menu to reset all preferences to their default state.</t>
+          <t>Click on the first adjustment option to apply changes to the column configuration.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -758,17 +706,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>F.3</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the 'Products' tab by clicking on the 'Products' option to access the product configuration section.</t>
+          <t>Click on the 'Save Preference' button to save the updated column configuration.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Products").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -778,17 +726,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Open the 'Products columns' configuration menu by clicking the button within the 'esp-card-component' element labeled 'Products columns (0)'.</t>
+          <t>Click on the first download button to initiate the file download and capture the downloaded file information for validation.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
+          <t>`page.locator(".icon-color-toolbar-active.zeb-download-underline").first.click()`</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -796,39 +744,26 @@
       <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>G.2</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>--- RESET PREFERENCES AND NAVIGATE TO PRODUCTS TAB ---</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Total (Plan Week)' column by checking its corresponding checkbox.</t>
+          <t>Click on the first adjustments button to open the adjustments menu. Look for the button identified by the '.pointer.zeb-adjustments' class.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -838,17 +773,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Base (Plan Week)' column by checking its corresponding checkbox.</t>
+          <t>Click on the 'Reset Preference' option to reset the preferences to their default state. Locate the option by its visible text.</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -858,17 +793,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Promotion (Plan Week)' column by checking its corresponding checkbox.</t>
+          <t>Click on the 'Products' tab to navigate to the product configuration section. Locate the tab by its visible text.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("Products").click()`</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -876,39 +811,26 @@
       <c r="F21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>G.6</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Enable visibility for the 'System Forecast Total (Plan+1)' column by checking its corresponding checkbox.</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>--- PRODUCTS COLUMN CONFIGURATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>G.7</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Base (Plan+1)' column by checking its corresponding checkbox.</t>
+          <t>Open the 'Products columns' configuration menu by clicking the button within the 'esp-card-component' element labeled 'Products columns (0)'.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -918,17 +840,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>G.8</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'System Forecast Promotion (Plan+1 Week)' column by checking its corresponding checkbox.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially. Locate the checkbox by its name.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan+1 Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -938,17 +860,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>G.9</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the 'Week Gross Units Average' column by checking its corresponding checkbox.</t>
+          <t>Enable visibility for the 'System Forecast Total (Plan Week)' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Week Gross Units Average Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -958,17 +880,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>G.10</t>
+          <t>H.4</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Enable visibility for the '6 Week Aged Net Units Average' column by checking its corresponding checkbox.</t>
+          <t>Enable visibility for the 'System Forecast Base (Plan Week)' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="6 Week Aged Net Units Average Column", exact=True).get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
@@ -978,17 +900,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>G.11</t>
+          <t>H.5</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Recheck the 'Toggle All Columns Visibility' checkbox to ensure all selected columns are visible.</t>
+          <t>Enable visibility for the 'System Forecast Promotion (Plan Week)' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -998,17 +920,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>G.12</t>
+          <t>H.6</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Click on the preferences dropdown menu to access options for saving or resetting preferences.</t>
+          <t>Enable visibility for the 'System Forecast Total (Plan+1)' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -1018,17 +940,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>G.13</t>
+          <t>H.7</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Save Preference' option to save the current column visibility settings.</t>
+          <t>Enable visibility for the 'System Forecast Base (Plan+1)' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan+1").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
@@ -1038,17 +960,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G.14</t>
+          <t>H.8</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Reopen the preferences dropdown menu to access the reset option.</t>
+          <t>Enable visibility for the 'System Forecast Promotion (Plan+1 Week)' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan+1 Week) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -1056,39 +978,26 @@
       <c r="F30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>G.15</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Reset Preference' option to revert to the default column visibility settings.</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN VISIBILITY MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon in the header to open the filter options for the column.</t>
+          <t>Enable visibility for the 'Week Gross Units Average' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="Week Gross Units Average Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1098,17 +1007,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>H.2</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Enter the filter value 'BARCEL' into the textbox to filter the column data.</t>
+          <t>Enable visibility for the '6 Week Aged Net Units Average' column by checking its corresponding checkbox. Locate the checkbox by its label.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("BARCEL")`</t>
+          <t>`page.get_by_role("treeitem", name="6 Week Aged Net Units Average Column", exact=True).get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1118,17 +1027,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>H.3</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the filter and update the displayed data.</t>
+          <t>Recheck the 'Toggle All Columns Visibility' checkbox to ensure all selected columns are visible. Locate the checkbox by its name.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1136,39 +1045,26 @@
       <c r="F34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>H.4</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Click on the filter icon in the header again to reopen the filter options.</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>--- PREFERENCE MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>H.5</t>
+          <t>J.1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Reset' button to clear the filter and revert the column data to its default state.</t>
+          <t>Open the preferences dropdown menu by clicking on the preferences icon to access options for saving or resetting preferences.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1178,17 +1074,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>H.6</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Select the row with the name 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
+          <t>Select the 'Save Preference' option from the dropdown menu to save the current column visibility settings.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1198,17 +1094,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>H.7</t>
+          <t>J.3</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the second page of the table by clicking on the pagination link labeled '2'.</t>
+          <t>Reopen the preferences dropdown menu by clicking on the preferences icon to access the reset option.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="2").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1218,17 +1114,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>H.8</t>
+          <t>J.4</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the third page of the table by clicking on the pagination link labeled '3'.</t>
+          <t>Select the 'Reset Preference' option from the dropdown menu to revert to the default column visibility settings.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="3").click()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1236,39 +1132,26 @@
       <c r="F39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>I.1</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Click on the fourth item in the list to select it.</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("listitem").filter(has_text=re.compile(r"^$")).nth(4).click()`</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN FILTERING ---</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>K.1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown caret to open the dropdown menu.</t>
+          <t>Click on the filter icon in the column header to open the filter options for that column.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".dropdown-caret.p-l-16").first.click()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1278,17 +1161,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Select the option 'View 20 row(s)' from the dropdown menu to adjust the number of rows displayed.</t>
+          <t>Enter the filter value 'BARCEL' into the textbox to filter the column data based on the input.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).nth(1).click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("BARCEL")`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1298,17 +1181,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter' button to open the filter options.</t>
+          <t>Click on the 'Apply' button to apply the filter and update the displayed data in the column.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Filter").click()`</t>
+          <t>`page.get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
@@ -1318,17 +1201,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>I.5</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret within the filter section to open the time filter options.</t>
+          <t>Click on the filter icon in the column header again to reopen the filter options for further actions.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1338,17 +1221,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>I.6</t>
+          <t>K.5</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 5 Next 4' option from the time filter dropdown.</t>
+          <t>Click on the 'Reset' button to clear the filter and revert the column data to its default state.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 4$")).nth(1).click()`</t>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1356,39 +1239,26 @@
       <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>I.7</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>--- ROW SELECTION AND PAGINATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>I.8</t>
+          <t>L.1</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 5 Next 12' option from the time filter dropdown.</t>
+          <t>Select the row with the name 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 12$")).nth(1).click()`</t>
+          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1398,17 +1268,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>I.9</t>
+          <t>L.2</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
+          <t>Navigate to the second page of the table by clicking on the pagination link labeled '2'.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("a").filter(has_text="2").click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1418,17 +1288,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>I.10</t>
+          <t>L.3</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 13 Next 4' option from the time filter dropdown.</t>
+          <t>Navigate to the third page of the table by clicking on the pagination link labeled '3'.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 4$")).nth(1).click()`</t>
+          <t>`page.locator("a").filter(has_text="3").click()`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1436,39 +1306,26 @@
       <c r="F49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>I.11</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>--- DROPDOWN AND ROW DISPLAY SETTINGS ---</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>I.12</t>
+          <t>M.1</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 13 Next 12' option from the time filter dropdown.</t>
+          <t>Click on the fourth item in the list to select it. Ensure the correct item is highlighted after selection.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 12$")).nth(1).click()`</t>
+          <t>`page.get_by_role("listitem").filter(has_text=re.compile(r"^$")).nth(4).click()`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1478,17 +1335,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>I.13</t>
+          <t>M.2</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to open the multi-select dropdown menu.</t>
+          <t>Open the dropdown menu by clicking on the first dropdown caret located on the left side of the screen.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".dropdown-caret.p-l-16").first.click()`</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1498,17 +1355,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>I.14</t>
+          <t>M.3</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Click on the first option in the dropdown menu to select it.</t>
+          <t>Adjust the number of rows displayed by selecting the 'View 20 row(s)' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1516,39 +1373,26 @@
       <c r="F53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>I.15</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first option under the 'dropdown-option' class to select it.</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>--- TIME FILTER SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>I.16</t>
+          <t>N.1</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Click on the second option in the dropdown menu to select it.</t>
+          <t>Click on the 'Filter' button to open the filter options.</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_text("Filter").click()`</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1558,17 +1402,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>I.17</t>
+          <t>N.2</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Click on the third option in the dropdown menu to select it.</t>
+          <t>Click on the dropdown caret within the filter section to open the time filter options.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(3) &gt; .d-flex").click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1578,17 +1422,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>I.18</t>
+          <t>N.3</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Click on the fourth option in the dropdown menu to select it.</t>
+          <t>Select the 'Latest 5 Next 4' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1598,17 +1442,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>I.19</t>
+          <t>N.4</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth option in the dropdown menu to select it.</t>
+          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1618,17 +1462,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>I.20</t>
+          <t>N.5</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Click on the sixth option in the dropdown menu to select it.</t>
+          <t>Select the 'Latest 5 Next 12' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(6)").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 5 Next 12$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1638,17 +1482,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>I.21</t>
+          <t>N.6</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Click on the first option in the dropdown menu again to deselect it.</t>
+          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
@@ -1658,17 +1502,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>J.1</t>
+          <t>N.7</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to open the multi-select dropdown menu for column visibility options.</t>
+          <t>Select the 'Latest 13 Next 4' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1678,17 +1522,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>N.8</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card to expand or collapse the product details.</t>
+          <t>Click on the dropdown caret within the filter section again to reopen the time filter options.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1698,17 +1542,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>J.3</t>
+          <t>N.9</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns in the Weekly Summary table.</t>
+          <t>Select the 'Latest 13 Next 12' option from the time filter dropdown.</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 12$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
@@ -1716,39 +1560,26 @@
       <c r="F63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>J.4</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Check the visibility of the column labeled '-10-26 (44)' by toggling its checkbox.</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="-10-26 (44) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>--- MULTI-SELECT DROPDOWN INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>J.5</t>
+          <t>O.1</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility of the column labeled '-11-02 (45)' by toggling its checkbox.</t>
+          <t>Click on the dropdown caret to open the multi-select dropdown menu.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="-11-02 (45) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1758,17 +1589,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>J.6</t>
+          <t>O.2</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility of the column labeled '-11-09 (46)' by toggling its checkbox.</t>
+          <t>Click on the first option in the dropdown menu to select it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="-11-09 (46) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -1778,17 +1609,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>J.7</t>
+          <t>O.3</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility of the column labeled '-11-16 (47)' by toggling its checkbox.</t>
+          <t>Click on the first option under the 'dropdown-option' class to select it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="-11-16 (47) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -1796,39 +1627,26 @@
       <c r="F67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>J.8</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Recheck the 'Toggle All Columns Visibility' checkbox to make all columns visible again in the Weekly Summary table.</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>--- DROPDOWN MENU OPTION SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>J.9</t>
+          <t>P.1</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card again to collapse the product details.</t>
+          <t>Click on the second option in the dropdown menu to select it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -1838,17 +1656,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>K.1</t>
+          <t>P.2</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' icon to open the dropdown menu for managing preferences.</t>
+          <t>Click on the third option in the dropdown menu to select it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(3) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -1858,17 +1676,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>K.2</t>
+          <t>P.3</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Save Preference' button to save the current table preferences.</t>
+          <t>Click on the fourth option in the dropdown menu to select it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(4)").click()`</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -1878,17 +1696,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>P.4</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Export' icon to initiate the export process for the table data.</t>
+          <t>Click on the fifth option in the dropdown menu to select it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -1898,17 +1716,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>P.5</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' dropdown to open the menu for managing preferences.</t>
+          <t>Click on the sixth option in the dropdown menu to select it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(6)").click()`</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr"/>
@@ -1918,17 +1736,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>K.5</t>
+          <t>P.6</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Select 'Reset Preference' from the dropdown to reset the table preferences to default.</t>
+          <t>Click on the first option in the dropdown menu again to deselect it. The specific option is not clear from the screenshot.</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -1936,39 +1754,26 @@
       <c r="F74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>K.6</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Click on the date '-02-15 (08)' to select it from the available options.</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("-02-15 (08)").click()`</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>--- WEEKLY SUMMARY COLUMN VISIBILITY MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>K.7</t>
+          <t>Q.1</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth image element to initiate the column visibility settings.</t>
+          <t>Click on the dropdown caret to open the multi-select dropdown menu for column visibility options.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("img").nth(5).click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
@@ -1978,17 +1783,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>K.8</t>
+          <t>Q.2</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Event Details columns (0)' card to open the column visibility options.</t>
+          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card to expand or collapse the product details.</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Event Details columns (0)").get_by_role("button").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
@@ -1998,17 +1803,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>K.9</t>
+          <t>Q.3</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Event Column' to hide it from the table.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns in the Weekly Summary table.</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -2018,17 +1823,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>K.10</t>
+          <t>Q.4</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'UPC 12 Column' to hide it from the table.</t>
+          <t>Check the visibility of the column labeled '-10-26 (44)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="UPC 12 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="-10-26 (44) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
@@ -2038,17 +1843,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>K.11</t>
+          <t>Q.5</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Customer Level 2 Column' to hide it from the table.</t>
+          <t>Check the visibility of the column labeled '-11-02 (45)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Customer Level 2 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="-11-02 (45) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -2058,17 +1863,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>K.12</t>
+          <t>Q.6</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Start Date Column' to hide it from the table.</t>
+          <t>Check the visibility of the column labeled '-11-09 (46)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Start Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="-11-09 (46) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -2078,17 +1883,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>K.13</t>
+          <t>Q.7</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'End Date Column' to hide it from the table.</t>
+          <t>Check the visibility of the column labeled '-11-16 (47)' by toggling its checkbox.</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="End Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="-11-16 (47) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -2098,12 +1903,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>K.14</t>
+          <t>Q.8</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
+          <t>Recheck the 'Toggle All Columns Visibility' checkbox to make all columns visible again in the Weekly Summary table.</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2118,17 +1923,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>K.15</t>
+          <t>Q.9</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' icon to open the dropdown menu for saving or resetting preferences.</t>
+          <t>Click on the button within the 'Weekly Summary Product:ARNOLD' card again to collapse the product details.</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Weekly Summary Product:ARNOLD").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -2136,39 +1941,26 @@
       <c r="F84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>K.16</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Click on 'Save Preference' to save the current column visibility settings.</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>--- PREFERENCE MANAGEMENT AND EXPORT ---</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>K.17</t>
+          <t>R.1</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Export' icon to export the data with the current preferences.</t>
+          <t>Click on the 'Preference' icon to open the dropdown menu for managing preferences.</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(6) &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
+          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2178,17 +1970,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>L.1</t>
+          <t>R.2</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Preference' icon to open the dropdown menu for resetting preferences.</t>
+          <t>Click on the 'Save Preference' button to save the current table preferences.</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_text("Save Preference").click()`</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
@@ -2198,17 +1990,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>L.2</t>
+          <t>R.3</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Reset Preference' to revert to the default column visibility settings.</t>
+          <t>Click on the 'Export' icon to initiate the export process for the table data.</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
@@ -2216,39 +2008,26 @@
       <c r="F88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>M.1</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Click on the filter icon in the column header to open the filter options.</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .ag-icon").click()`</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>--- RESET PREFERENCES AND DATE SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>M.2</t>
+          <t>S.1</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Enter 'Scan Track' into the filter textbox to filter the data based on this value.</t>
+          <t>Click on the 'Preference' dropdown to open the menu for managing preferences.</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("Scan Track")`</t>
+          <t>`page.locator("div:nth-child(4) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
@@ -2258,17 +2037,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>M.3</t>
+          <t>S.2</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the filter and update the displayed data.</t>
+          <t>Select 'Reset Preference' from the dropdown to reset the table preferences to default.</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
@@ -2278,17 +2057,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>M.4</t>
+          <t>S.3</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Click on the active filter icon to open the filter options for resetting.</t>
+          <t>Click on the date '-02-15 (08)' to select it from the available options.</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button.ag-filter-active &gt; .ag-icon").click()`</t>
+          <t>`page.get_by_text("-02-15 (08)").click()`</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr"/>
@@ -2296,39 +2075,26 @@
       <c r="F92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>M.5</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Reset' button to clear the applied filter and restore the unfiltered data.</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>--- EVENT DETAILS COLUMN VISIBILITY MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>N.1</t>
+          <t>T.1</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Products' tab to navigate to the product selection view.</t>
+          <t>Click on the fifth image element to open the column visibility settings for 'Event Details'.</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Products").click()`</t>
+          <t>`page.get_by_role("img").nth(5).click()`</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
@@ -2338,17 +2104,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>N.2</t>
+          <t>T.2</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Double-click on the product 'ARNOLD-BRWNBRY-OROWT' to drill down into its details.</t>
+          <t>Click on the button within the 'Event Details columns (0)' card to access the column visibility options.</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="ARNOLD-BRWNBRY-OROWT").first.dblclick()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Event Details columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
@@ -2358,17 +2124,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>N.3</t>
+          <t>T.3</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Double-click on 'ABO COUNTRY' to further drill down into its details.</t>
+          <t>Uncheck the 'Event Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.dblclick()`</t>
+          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
@@ -2378,17 +2144,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>N.4</t>
+          <t>T.4</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Click on 'ABO COUNTRY' to select it.</t>
+          <t>Uncheck the 'UPC 12 Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="UPC 12 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
@@ -2398,17 +2164,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>N.5</t>
+          <t>T.5</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Double-click on the second instance of 'ABO COUNTRY' to drill down further.</t>
+          <t>Uncheck the 'Customer Level 2 Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("ABO COUNTRY").nth(1).dblclick()`</t>
+          <t>`page.get_by_role("treeitem", name="Customer Level 2 Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
@@ -2418,17 +2184,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>N.6</t>
+          <t>T.6</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Right-click on the product 'OR CTY BTRMK WP 24Z-731300012500' to open the context menu.</t>
+          <t>Uncheck the 'Start Date Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text=re.compile(r"^OR CTY BTRMK WP 24Z-731300012500$")).click(button="right")`</t>
+          <t>`page.get_by_role("treeitem", name="Start Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
@@ -2438,17 +2204,17 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>N.7</t>
+          <t>T.7</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Drill up' from the context menu to navigate back to the previous level.</t>
+          <t>Uncheck the 'End Date Column' to hide it from the table.</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Drill up").click()`</t>
+          <t>`page.get_by_role("treeitem", name="End Date Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -2456,39 +2222,26 @@
       <c r="F100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>N.8</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Right-click on 'ABO COUNTRY' to open the context menu again.</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr"/>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>--- TOGGLE ALL COLUMNS VISIBILITY AND SAVE PREFERENCES ---</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>N.9</t>
+          <t>U.1</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Drill up' from the context menu to navigate back another level.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Drill up").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
@@ -2498,17 +2251,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>N.10</t>
+          <t>U.2</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Right-click on 'ABO COUNTRY' to open the context menu once more.</t>
+          <t>Click on the 'Preference' icon to open the dropdown menu for saving or resetting preferences.</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
+          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
@@ -2518,17 +2271,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>N.11</t>
+          <t>U.3</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Drill up' from the context menu to return to the top level.</t>
+          <t>Click on 'Save Preference' to save the current column visibility settings.</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Drill up").click()`</t>
+          <t>`page.get_by_text("Save Preference").click()`</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
@@ -2536,39 +2289,26 @@
       <c r="F104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>O.1</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Select the row for the product 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="4" t="inlineStr"/>
-      <c r="F105" s="4" t="inlineStr"/>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>--- EXPORT DATA WITH CURRENT PREFERENCES ---</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>O.2</t>
+          <t>V.1</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Close the current page after completing the row selection.</t>
+          <t>Click on the 'Export' icon to export the data with the current preferences.</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>`page.close()`</t>
+          <t>`page.locator("div:nth-child(6) &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr"/>
@@ -2576,48 +2316,460 @@
       <c r="F106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>O.3</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Close the browser context to clean up resources.</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>`context.close()`</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>--- RESET PREFERENCES TO DEFAULT ---</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>O.4</t>
+          <t>W.1</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Close the browser to end the session.</t>
+          <t>Click on the 'Preference' icon to open the dropdown menu for resetting preferences.</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>`browser.close()`</t>
+          <t>`page.locator(".col-12.m-t-16 &gt; div &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .title &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>W.2</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'Reset Preference' to revert to the default column visibility settings.</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>--- APPLY AND RESET COLUMN FILTERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>X.1</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Click on the filter icon in the column header to open the filter options.</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .ag-icon").click()`</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>X.2</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Enter 'Scan Track' into the filter textbox to filter the data based on this value.</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("Scan Track")`</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>X.3</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Apply' button to apply the filter and update the displayed data.</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Apply").click()`</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>X.4</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Click on the active filter icon to open the filter options for resetting.</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button.ag-filter-active &gt; .ag-icon").click()`</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>X.5</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Reset' button to clear the applied filter and restore the unfiltered data.</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>--- DRILL DOWN AND DRILL UP NAVIGATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Y.1</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Products' tab to navigate to the product selection view.</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Products").click()`</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Y.2</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Double-click on the product 'ARNOLD-BRWNBRY-OROWT' to drill down into its details.</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="ARNOLD-BRWNBRY-OROWT").first.dblclick()`</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Y.3</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Double-click on 'ABO COUNTRY' to further drill down into its details.</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.dblclick()`</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Y.4</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'ABO COUNTRY' to select it.</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click()`</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Y.5</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Double-click on the second instance of 'ABO COUNTRY' to drill down further.</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("ABO COUNTRY").nth(1).dblclick()`</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Y.6</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Right-click on the product 'OR CTY BTRMK WP 24Z-731300012500' to open the context menu.</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text=re.compile(r"^OR CTY BTRMK WP 24Z-731300012500$")).click(button="right")`</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Y.7</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'Drill up' from the context menu to navigate back to the previous level.</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Drill up").click()`</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Y.8</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Right-click on 'ABO COUNTRY' to open the context menu again.</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Y.9</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'Drill up' from the context menu to navigate back another level.</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Drill up").click()`</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Y.10</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Right-click on 'ABO COUNTRY' to open the context menu once more.</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="ABO COUNTRY").first.click(button="right")`</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Y.11</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'Drill up' from the context menu to return to the top level.</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Drill up").click()`</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>--- ROW SELECTION AND PAGE CLOSURE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Z.1</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Select the row for the product 'ARNOLD-BRWNBRY-OROWT' by toggling the checkbox in the grid cell.</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Z.2</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Close the current page after completing the row selection.</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>`page.close()`</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="25">
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A110:F110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
